--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113293579</v>
+        <v>113293554</v>
       </c>
       <c r="B2" t="n">
-        <v>55984</v>
+        <v>55987</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600006</v>
+        <v>599871</v>
       </c>
       <c r="R2" t="n">
-        <v>6954386</v>
+        <v>6954450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113293554</v>
+        <v>113293579</v>
       </c>
       <c r="B3" t="n">
-        <v>55987</v>
+        <v>55984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599871</v>
+        <v>600006</v>
       </c>
       <c r="R3" t="n">
-        <v>6954450</v>
+        <v>6954386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113293554</v>
+        <v>113293579</v>
       </c>
       <c r="B2" t="n">
-        <v>55987</v>
+        <v>55985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599871</v>
+        <v>600006</v>
       </c>
       <c r="R2" t="n">
-        <v>6954450</v>
+        <v>6954386</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113293579</v>
+        <v>113293554</v>
       </c>
       <c r="B3" t="n">
-        <v>55984</v>
+        <v>55988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600006</v>
+        <v>599871</v>
       </c>
       <c r="R3" t="n">
-        <v>6954386</v>
+        <v>6954450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113293579</v>
+        <v>113293554</v>
       </c>
       <c r="B2" t="n">
-        <v>55985</v>
+        <v>55988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600006</v>
+        <v>599871</v>
       </c>
       <c r="R2" t="n">
-        <v>6954386</v>
+        <v>6954450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113293554</v>
+        <v>113293579</v>
       </c>
       <c r="B3" t="n">
-        <v>55988</v>
+        <v>55985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599871</v>
+        <v>600006</v>
       </c>
       <c r="R3" t="n">
-        <v>6954450</v>
+        <v>6954386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113293554</v>
+        <v>113293579</v>
       </c>
       <c r="B2" t="n">
-        <v>55988</v>
+        <v>55985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599871</v>
+        <v>600006</v>
       </c>
       <c r="R2" t="n">
-        <v>6954450</v>
+        <v>6954386</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113293579</v>
+        <v>113293554</v>
       </c>
       <c r="B3" t="n">
-        <v>55985</v>
+        <v>55988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600006</v>
+        <v>599871</v>
       </c>
       <c r="R3" t="n">
-        <v>6954386</v>
+        <v>6954450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113293579</v>
       </c>
       <c r="B2" t="n">
-        <v>55985</v>
+        <v>55988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>113293554</v>
       </c>
       <c r="B3" t="n">
-        <v>55988</v>
+        <v>55991</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113293579</v>
+        <v>113293554</v>
       </c>
       <c r="B2" t="n">
-        <v>55988</v>
+        <v>55995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600006</v>
+        <v>599871</v>
       </c>
       <c r="R2" t="n">
-        <v>6954386</v>
+        <v>6954450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113293554</v>
+        <v>113293579</v>
       </c>
       <c r="B3" t="n">
-        <v>55991</v>
+        <v>55992</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599871</v>
+        <v>600006</v>
       </c>
       <c r="R3" t="n">
-        <v>6954450</v>
+        <v>6954386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113293554</v>
+        <v>113293579</v>
       </c>
       <c r="B2" t="n">
-        <v>55995</v>
+        <v>55992</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599871</v>
+        <v>600006</v>
       </c>
       <c r="R2" t="n">
-        <v>6954450</v>
+        <v>6954386</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113293579</v>
+        <v>113293554</v>
       </c>
       <c r="B3" t="n">
-        <v>55992</v>
+        <v>55995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600006</v>
+        <v>599871</v>
       </c>
       <c r="R3" t="n">
-        <v>6954386</v>
+        <v>6954450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113293579</v>
       </c>
       <c r="B2" t="n">
-        <v>55992</v>
+        <v>55999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>113293554</v>
       </c>
       <c r="B3" t="n">
-        <v>55995</v>
+        <v>56002</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 46214-2022 artfynd.xlsx
+++ b/artfynd/A 46214-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
